--- a/data/trans_camb/P1428-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1428-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,81</t>
+          <t>-3,5</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,59</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-2,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,26; -1,0</t>
+          <t>-7,02; -1,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -4,71</t>
+          <t>-10,49; -4,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,5</t>
+          <t>-6,67; -0,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,11; -7,17</t>
+          <t>-14,42; -7,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,4; -10,58</t>
+          <t>-18,31; -10,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 2,22</t>
+          <t>-6,19; 1,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,76; -4,93</t>
+          <t>-9,8; -5,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-13,75; -8,5</t>
+          <t>-13,7; -8,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 1,23</t>
+          <t>-4,79; 0,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-17,92%</t>
+          <t>-22,36%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-4,49%</t>
+          <t>-6,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-5,25%</t>
+          <t>-8,77%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,05; -6,67</t>
+          <t>-41,31; -6,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,38; -33,37</t>
+          <t>-61,4; -32,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,32; 3,73</t>
+          <t>-38,77; -0,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-38,11; -21,31</t>
+          <t>-38,64; -21,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,99; -31,42</t>
+          <t>-49,06; -32,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 6,57</t>
+          <t>-16,74; 3,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,94; -19,16</t>
+          <t>-35,33; -19,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-49,67; -32,88</t>
+          <t>-49,94; -34,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 4,66</t>
+          <t>-17,23; 1,31</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,98</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,64</t>
+          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,17</t>
+          <t>-2,16; 0,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,42; -0,09</t>
+          <t>-2,35; -0,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,66</t>
+          <t>-0,42; 1,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; -0,07</t>
+          <t>-3,44; -0,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,11</t>
+          <t>-3,1; 0,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 33,33</t>
+          <t>1,4; 4,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; -0,38</t>
+          <t>-2,48; -0,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; -0,32</t>
+          <t>-2,35; -0,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 21,26</t>
+          <t>0,82; 2,81</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>163,5%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>110,28%</t>
+          <t>36,12%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,69; 5,65</t>
+          <t>-50,65; 4,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,25; -2,11</t>
+          <t>-55,47; -3,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 54,08</t>
+          <t>-11,2; 68,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,66; -0,84</t>
+          <t>-44,97; 0,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,48; 2,45</t>
+          <t>-40,23; 4,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,12; 559,81</t>
+          <t>17,27; 78,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,46; -8,3</t>
+          <t>-43,18; -9,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,63; -6,26</t>
+          <t>-40,31; -6,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,04; 433,79</t>
+          <t>13,49; 61,62</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>2,28</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>1,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,27</t>
+          <t>-2,26; 2,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 1,3</t>
+          <t>-2,73; 1,09</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,8</t>
+          <t>-1,79; 1,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 3,03</t>
+          <t>-3,2; 2,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 0,11</t>
+          <t>-4,91; 0,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,74</t>
+          <t>-0,43; 4,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,78</t>
+          <t>-1,93; 1,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 0,18</t>
+          <t>-2,95; 0,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,82</t>
+          <t>-0,24; 2,9</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,43; 168,56</t>
+          <t>-68,2; 134,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-75,57; 104,02</t>
+          <t>-77,59; 76,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,74; 133,76</t>
+          <t>-48,01; 124,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-50,04; 73,33</t>
+          <t>-48,33; 70,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,74; 7,72</t>
+          <t>-71,97; 15,39</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 125,96</t>
+          <t>-6,22; 119,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,97; 61,02</t>
+          <t>-43,35; 66,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,59; 9,48</t>
+          <t>-62,55; 8,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,21; 96,26</t>
+          <t>-5,0; 104,7</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,18</t>
+          <t>-1,95</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,48</t>
+          <t>-3,28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>-2,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,32; -0,85</t>
+          <t>-3,26; -0,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -2,37</t>
+          <t>-4,71; -2,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; -1,01</t>
+          <t>-3,06; -0,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,03; -3,6</t>
+          <t>-6,99; -3,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,87; -6,52</t>
+          <t>-10,05; -6,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 16,04</t>
+          <t>-4,86; -1,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,62; -2,42</t>
+          <t>-4,69; -2,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; -4,93</t>
+          <t>-7,02; -4,98</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,99</t>
+          <t>-3,57; -1,57</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-30,2%</t>
+          <t>-27,0%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>-18,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,92%</t>
+          <t>-20,54%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-42,04; -12,68</t>
+          <t>-41,77; -14,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-60,24; -37,37</t>
+          <t>-60,34; -38,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-46,65; -15,56</t>
+          <t>-39,57; -13,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,46; -21,47</t>
+          <t>-38,01; -21,26</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,06; -38,85</t>
+          <t>-54,06; -39,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 95,13</t>
+          <t>-26,07; -10,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-35,66; -20,59</t>
+          <t>-36,23; -22,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-53,63; -41,51</t>
+          <t>-53,59; -41,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 73,01</t>
+          <t>-26,93; -13,12</t>
         </is>
       </c>
     </row>
